--- a/translations/welsh-translations/00-shared-layout.xlsx
+++ b/translations/welsh-translations/00-shared-layout.xlsx
@@ -163,10 +163,10 @@
     <t>common.phaseBanner.lead</t>
   </si>
   <si>
-    <t xml:space="preserve">This is a new service - your </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mae hwn yn wasanaeth newydd – bydd eich </t>
+    <t>This is a new service - your</t>
+  </si>
+  <si>
+    <t>Mae hwn yn wasanaeth newydd – bydd eich</t>
   </si>
   <si>
     <t>common.phaseBanner.feedbackLink</t>
@@ -181,10 +181,10 @@
     <t>common.phaseBanner.leadAfterLink</t>
   </si>
   <si>
-    <t xml:space="preserve"> will help us to improve it.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> yn ein helpu i’w wella.</t>
+    <t>will help us to improve it.</t>
+  </si>
+  <si>
+    <t>yn ein helpu i’w wella.</t>
   </si>
   <si>
     <t>common.languageSwitcher.label</t>
